--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488088_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488088_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4961</v>
+        <v>2.1063</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3062</v>
+        <v>2.0006</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1899</v>
+        <v>0.1056</v>
       </c>
       <c r="G2" t="n">
         <v>1.4877</v>
@@ -610,13 +610,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0084</v>
+        <v>0.6185</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7526</v>
+        <v>0.447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>G. CABRERA RUIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5834</v>
+        <v>1.2862</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1679</v>
+        <v>-0.8756</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4155</v>
+        <v>2.1617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5409</v>
+        <v>-0.162</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6147</v>
+        <v>0.4656</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1556</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.012</v>
+        <v>-0.5848</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6186</v>
+        <v>0.7333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6066</v>
+        <v>-1.3181</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4228</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0039</v>
+        <v>-0.2677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.549</v>
+        <v>0.6905</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5947</v>
+        <v>2.1805</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5947</v>
+        <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4478</v>
+        <v>-0.5331</v>
       </c>
       <c r="T3" t="n">
-        <v>0.18</v>
+        <v>-0.2908</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2679</v>
+        <v>-0.2423</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.1992</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6057</v>
+        <v>1.0988</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0206</v>
+        <v>-0.0358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6262</v>
+        <v>1.1347</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8228</v>
+        <v>0.5409</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0197</v>
+        <v>-0.6147</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8425</v>
+        <v>1.1556</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2057</v>
+        <v>-0.012</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8771</v>
+        <v>-0.6186</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6713</v>
+        <v>0.6066</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0285</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8574000000000001</v>
+        <v>0.0039</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1711</v>
+        <v>0.549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3787</v>
+        <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2856</v>
+        <v>-0.0367</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0438</v>
+        <v>-0.0238</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3294</v>
+        <v>-0.0129</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7464</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CABRERA RUIZ</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5522</v>
+        <v>0.3027</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3849</v>
+        <v>0.3027</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9371</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.162</v>
+        <v>0.3027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4656</v>
+        <v>0.3027</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5848</v>
+        <v>0.3027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7333</v>
+        <v>0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3181</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4228</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2677</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6905</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2671</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8001</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.467</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1992</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3027</v>
+        <v>0.1898</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3027</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.2893</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3027</v>
+        <v>-0.8228</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3027</v>
+        <v>1.0197</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.8425</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3027</v>
+        <v>1.2057</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3027</v>
+        <v>1.8771</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6713</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.0285</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.1711</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.1303</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1227</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0076</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.7464</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5939</v>
+        <v>-0.334</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5653</v>
+        <v>-0.3616</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0285</v>
+        <v>0.0276</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7047</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1109</v>
+        <v>0.3708</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.2772</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7173</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1031</v>
+        <v>-0.4903</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8204</v>
+        <v>-0.1795</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0588</v>
+        <v>-0.9012</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4833</v>
+        <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>1.542</v>
+        <v>-1.0503</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1579</v>
+        <v>0.9312</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4163</v>
+        <v>1.0763</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5742</v>
+        <v>-0.1451</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-1.8324</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.067</v>
+        <v>-0.9272</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9679</v>
+        <v>-0.9052</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4219</v>
+        <v>-0.647</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9363</v>
+        <v>-0.0934</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5144</v>
+        <v>-0.5536</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5944</v>
+        <v>0.2837</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5944</v>
+        <v>0.6206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0826</v>
+        <v>-1.2318</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8189</v>
+        <v>-0.3833</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2638</v>
+        <v>-0.8485</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9012</v>
+        <v>0.0588</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1491</v>
+        <v>-1.4833</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0503</v>
+        <v>1.542</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9312</v>
+        <v>0.1579</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0763</v>
+        <v>-0.4163</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1451</v>
+        <v>0.5742</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8324</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9272</v>
+        <v>-1.067</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9052</v>
+        <v>0.9679</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0598</v>
+        <v>-0.0926</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.422</v>
+        <v>0.4499</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6378</v>
+        <v>-0.5425</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2837</v>
+        <v>-1.5944</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6206</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9079</v>
+        <v>-1.4172</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2278</v>
+        <v>-0.9617</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6801</v>
+        <v>-0.4555</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5727</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0065</v>
+        <v>-0.5157</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.11</v>
+        <v>0.1562</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8965</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3199</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4038</v>
+        <v>-2.804</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.186</v>
+        <v>-2.6143</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2178</v>
+        <v>-0.1897</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4265</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8586</v>
+        <v>-0.2588</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7267</v>
+        <v>-0.155</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1319</v>
+        <v>-0.1039</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3169</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5587</v>
+        <v>-3.1447</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6004</v>
+        <v>-3.2815</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9583</v>
+        <v>0.1368</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3251</v>
+        <v>-3.7017</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5093</v>
+        <v>-2.8484</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8158</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3301</v>
+        <v>-2.9117</v>
       </c>
       <c r="K12" t="n">
-        <v>0.29</v>
+        <v>-2.313</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0402</v>
+        <v>-0.5988</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6552</v>
+        <v>-0.79</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7993</v>
+        <v>-0.5355</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.856</v>
+        <v>-0.2545</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4236</v>
+        <v>-0.434</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7674</v>
+        <v>-0.3697</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6562</v>
+        <v>-0.0643</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8731</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6811</v>
+        <v>-4.4444</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6495</v>
+        <v>-3.1492</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0317</v>
+        <v>-1.2952</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.7017</v>
+        <v>-2.3251</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8484</v>
+        <v>-0.5093</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-1.8158</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9117</v>
+        <v>0.3301</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.313</v>
+        <v>0.29</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5988</v>
+        <v>0.0402</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.79</v>
+        <v>-2.6552</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5355</v>
+        <v>-0.7993</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2545</v>
+        <v>-1.856</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9705</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7377</v>
+        <v>0.2186</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2328</v>
+        <v>0.3192</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.8731</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.1397</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.7562</v>
+        <v>-4.4754</v>
       </c>
       <c r="E14" t="n">
         <v>-4.1802</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5759</v>
+        <v>-0.2952</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6021</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3523</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2348</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1176</v>
+        <v>0.1632</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-14.1614</v>
+        <v>-13.5376</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.7537</v>
+        <v>-14.1297</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5921999999999993</v>
+        <v>0.5921000000000002</v>
       </c>
       <c r="G15" t="n">
         <v>-12.8287</v>
@@ -1603,10 +1603,10 @@
         <v>-1.2052</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.2172</v>
+        <v>-4.217199999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.4063</v>
+        <v>-7.406299999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-6.304799999999999</v>
@@ -1624,13 +1624,13 @@
         <v>14.8669</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8166</v>
+        <v>-1.1926</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3653999999999999</v>
+        <v>0.2586999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4513</v>
+        <v>-1.4514</v>
       </c>
       <c r="V15" t="n">
         <v>-3.4805</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.0863</v>
+        <v>7.3861</v>
       </c>
       <c r="E16" t="n">
         <v>5.4177</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6686</v>
+        <v>1.9684</v>
       </c>
       <c r="G16" t="n">
         <v>4.7506</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6024</v>
+        <v>0.9021</v>
       </c>
       <c r="T16" t="n">
         <v>0.2975</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3049</v>
+        <v>0.6046</v>
       </c>
       <c r="V16" t="n">
         <v>0.9405</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. GARCIA GAZQUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1309</v>
+        <v>4.6684</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5709</v>
+        <v>0.4225</v>
       </c>
       <c r="F17" t="n">
-        <v>2.56</v>
+        <v>4.246</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2948</v>
+        <v>3.2236</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5241</v>
+        <v>3.1396</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0225</v>
+        <v>1.4832</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0138</v>
+        <v>-0.4168</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0363</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3173</v>
+        <v>1.7404</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7569</v>
+        <v>0.5009</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5604</v>
+        <v>1.2395</v>
       </c>
       <c r="P17" t="n">
         <v>-0.1982</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>3.0343</v>
+        <v>0.8433</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5845</v>
+        <v>-0.1448</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4498</v>
+        <v>0.9881</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0663</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GARCIA GAZQUEZ</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.926</v>
+        <v>2.6371</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1887</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1147</v>
+        <v>3.5034</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2236</v>
+        <v>1.077</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.4174</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1396</v>
+        <v>1.4944</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4832</v>
+        <v>-0.3765</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4168</v>
+        <v>-0.2352</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>-0.1413</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7404</v>
+        <v>1.4535</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5009</v>
+        <v>-0.1822</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2395</v>
+        <v>1.6356</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1008</v>
+        <v>-0.0257</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.756</v>
+        <v>-0.4899</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8568</v>
+        <v>0.4642</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0663</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.129</v>
+        <v>2.3456</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0701</v>
+        <v>0.0429</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1991</v>
+        <v>2.3027</v>
       </c>
       <c r="G20" t="n">
-        <v>1.077</v>
+        <v>1.2948</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4174</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4944</v>
+        <v>0.5241</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3765</v>
+        <v>-0.0225</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2352</v>
+        <v>0.0138</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1413</v>
+        <v>-0.0363</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4535</v>
+        <v>1.3173</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1822</v>
+        <v>0.7569</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6356</v>
+        <v>0.5604</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5858</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5337</v>
+        <v>1.249</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6936</v>
+        <v>1.0564</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1599</v>
+        <v>0.1925</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6477</v>
+        <v>2.3183</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2841</v>
+        <v>0.0215</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9319</v>
+        <v>2.2969</v>
       </c>
       <c r="G21" t="n">
         <v>2.0415</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6009</v>
+        <v>0.0697</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4368</v>
+        <v>-0.1312</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1641</v>
+        <v>0.2009</v>
       </c>
       <c r="V21" t="n">
         <v>0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5451</v>
+        <v>1.6646</v>
       </c>
       <c r="E22" t="n">
-        <v>1.478</v>
+        <v>1.2742</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.3903</v>
       </c>
       <c r="G22" t="n">
         <v>1.8911</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3696</v>
+        <v>0.4891</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6095</v>
+        <v>0.4058</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2399</v>
+        <v>0.0833</v>
       </c>
       <c r="V22" t="n">
         <v>0.8701</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.0461</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0834</v>
+        <v>-1.8984</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6212</v>
+        <v>1.9444</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0822</v>
@@ -2248,13 +2248,13 @@
         <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>0.946</v>
+        <v>0.4543</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2886</v>
+        <v>0.4737</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3426</v>
+        <v>-0.0194</v>
       </c>
       <c r="V23" t="n">
         <v>0.674</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9651</v>
+        <v>-0.6244</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2735</v>
+        <v>-2.5605</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3085</v>
+        <v>1.936</v>
       </c>
       <c r="G24" t="n">
         <v>1.3294</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2507</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1232</v>
+        <v>-0.4101</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1276</v>
+        <v>0.5</v>
       </c>
       <c r="V24" t="n">
         <v>0.5331</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9897</v>
+        <v>-2.3282</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2606</v>
+        <v>-2.955</v>
       </c>
       <c r="F25" t="n">
-        <v>0.271</v>
+        <v>0.6268</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1795</v>
@@ -2404,13 +2404,13 @@
         <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0173</v>
+        <v>0.6442</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0072</v>
+        <v>0.2984</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.01</v>
+        <v>0.3459</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3026</v>
+        <v>-3.6515</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3143</v>
+        <v>-1.9068</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9883</v>
+        <v>-1.7447</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9337</v>
@@ -2482,13 +2482,13 @@
         <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8337</v>
+        <v>-0.1826</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.312</v>
+        <v>0.0955</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.2781</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9405</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>14.1614</v>
+        <v>16.8781</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5921000000000007</v>
+        <v>-0.5923000000000003</v>
       </c>
       <c r="F27" t="n">
-        <v>14.7538</v>
+        <v>17.4702</v>
       </c>
       <c r="G27" t="n">
         <v>12.8286</v>
@@ -2533,7 +2533,7 @@
         <v>5.319099999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>7.406300000000001</v>
+        <v>7.406299999999997</v>
       </c>
       <c r="K27" t="n">
         <v>6.3046</v>
@@ -2548,7 +2548,7 @@
         <v>1.2051</v>
       </c>
       <c r="O27" t="n">
-        <v>4.217300000000001</v>
+        <v>4.2173</v>
       </c>
       <c r="P27" t="n">
         <v>-3.9644</v>
@@ -2560,13 +2560,13 @@
         <v>10.9022</v>
       </c>
       <c r="S27" t="n">
-        <v>1.816800000000001</v>
+        <v>4.5333</v>
       </c>
       <c r="T27" t="n">
-        <v>1.451299999999999</v>
+        <v>1.4513</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3654999999999999</v>
+        <v>3.082</v>
       </c>
       <c r="V27" t="n">
         <v>3.4805</v>
